--- a/assessment_forms/039_master_data_governance_knowledge_quiz--assessment_forms.xlsx
+++ b/assessment_forms/039_master_data_governance_knowledge_quiz--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_page_1</t>
+          <t>what_is_data_governance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>what_is_data_governance</t>
+          <t>What is data governance?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>form_page_2</t>
+          <t>organizational_challenges</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>organizational_challenges</t>
+          <t>What are some organizational challenges that data governance addresses?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>form_page_3</t>
+          <t>training_programs</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>training_programs</t>
+          <t>What are some training programs offered for data governance?</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>form_page_4</t>
+          <t>data_quality_control</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>data_quality_control</t>
+          <t>What are some data quality control practices?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>form_page_5</t>
+          <t>data_security</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>data_security</t>
+          <t>What are some data security measures?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>form_page_6</t>
+          <t>data_privacy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>data_privacy</t>
+          <t>What are some data privacy practices?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>form_page_7</t>
+          <t>data_architecture</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>data_architecture</t>
+          <t>What is data architecture?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>form_page_8</t>
+          <t>data_management</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>data_management</t>
+          <t>What is data management?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>form_page_9</t>
+          <t>data_warehouse</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>data_warehouse</t>
+          <t>What is a data warehouse?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>form_page_10</t>
+          <t>data_lifecycle</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>data_lifecycle</t>
+          <t>What is data lifecycle management?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>form_page_11</t>
+          <t>data_quality_measures</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>data_quality_measures</t>
+          <t>What are some data quality measures?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>form_page_12</t>
+          <t>data_lineage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>data_lineage</t>
+          <t>What is data lineage?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>form_page_13</t>
+          <t>data_security_practices</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>data_security_practices</t>
+          <t>What are some data security practices?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>form_page_14</t>
+          <t>data_privacy_practices</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>data_privacy_practices</t>
+          <t>Data Privacy Practices</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>form_page_15</t>
+          <t>data_disaster_recovery</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>data_disaster_recovery</t>
+          <t>What is data disaster recovery?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>form_page_16</t>
+          <t>data_architecture_practices</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>data_architecture_practices</t>
+          <t>What are some data architecture practices?</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>form_page_17</t>
+          <t>data_management_practices</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>data_management_practices</t>
+          <t>What are some data management practices?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>form_page_18</t>
+          <t>master_data_catalog</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>master_data_catalog</t>
+          <t>What is the master data catalog?</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>form_page_19</t>
+          <t>data_lineage_practices</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>data_lineage_practices</t>
+          <t>What are some data lineage practices?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_page_20</t>
+          <t>data_quality_control_practices</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>data_quality_control_practices</t>
+          <t>Data Quality Control Practices</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>form_page_21</t>
+          <t>data_disaster_recovery_practices</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>data_disaster_recovery_practices</t>
+          <t>What are some data disaster recovery practices?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>form_page_22</t>
+          <t>data_architecture_practices_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>data_architecture_practices</t>
+          <t>Data Architecture Practices 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>form_page_23</t>
+          <t>data_management_practices_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>data_management_practices</t>
+          <t>Data Management Practices 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>form_page_24</t>
+          <t>data_security_practices_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>data_security_practices</t>
+          <t>Data Security Practices 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_page_25</t>
+          <t>data_privacy_practices_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>data_privacy_practices</t>
+          <t>Data Privacy Practices 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,168 +1126,219 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>form_page_3_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>data_governance_101</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Data Governance 101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>form_page_3_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>data_governance_masterclass</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Data Governance Masterclass</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>form_page_4_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>data_governance_bootcamp</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Good</t>
+          <t>Data Governance Bootcamp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>form_page_4_choices</t>
+          <t>training_programs_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>data_governance_certification</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Poor</t>
+          <t>Data Governance Certification</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>form_page_5_choices</t>
+          <t>data_quality_control_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>form_page_5_choices</t>
+          <t>data_quality_control_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>form_page_7_choices</t>
+          <t>data_quality_control_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>form_page_7_choices</t>
+          <t>data_security_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>form_page_8_choices</t>
+          <t>data_security_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>form_page_8_choices</t>
+          <t>data_architecture_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>data_architecture_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>data_management_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>data_management_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>No</t>
         </is>
